--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,2119 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131389082</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457338</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7080487</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131389099</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7080505</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131389048</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>457237</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7080435</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131389085</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>457010</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7080480</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131389084</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>457252</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7080519</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131389055</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>457004</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7080486</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131389097</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>457310</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7080547</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131389044</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>457358</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7080415</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131389047</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>457342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7080396</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131389045</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>457287</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7080550</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131389086</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>456992</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7080516</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131389046</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>457268</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7080539</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131389059</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>456981</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7080514</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131389043</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>456992</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7080517</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131389053</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>457007</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7080483</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131389054</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>457005</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7080485</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131389061</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>456959</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7080532</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131389060</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>456972</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7080521</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131389100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>457233</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7080474</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131389083</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91834</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>457266</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7080540</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131389098</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>457039</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7080517</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389099</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389048</v>
+        <v>131389085</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,23 +988,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1012,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457237</v>
+        <v>457010</v>
       </c>
       <c r="R5" t="n">
-        <v>7080435</v>
+        <v>7080480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,11 +1044,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389085</v>
+        <v>131389048</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,19 +1081,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1110,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457010</v>
+        <v>457237</v>
       </c>
       <c r="R6" t="n">
-        <v>7080480</v>
+        <v>7080435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1141,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131389097</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389044</v>
+        <v>131389047</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457358</v>
+        <v>457342</v>
       </c>
       <c r="R10" t="n">
-        <v>7080415</v>
+        <v>7080396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389047</v>
+        <v>131389044</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457342</v>
+        <v>457358</v>
       </c>
       <c r="R11" t="n">
-        <v>7080396</v>
+        <v>7080415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
         <v>131389045</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389059</v>
+        <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,16 +2007,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456981</v>
+        <v>456992</v>
       </c>
       <c r="R15" t="n">
-        <v>7080514</v>
+        <v>7080517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,14 +2061,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2080,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389043</v>
+        <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,24 +2117,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456992</v>
+        <v>456981</v>
       </c>
       <c r="R16" t="n">
-        <v>7080517</v>
+        <v>7080514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>131389053</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>131389054</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389061</v>
+        <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,23 +2405,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2429,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456959</v>
+        <v>457266</v>
       </c>
       <c r="R19" t="n">
-        <v>7080532</v>
+        <v>7080540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2461,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389060</v>
+        <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,21 +2498,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2531,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456972</v>
+        <v>457233</v>
       </c>
       <c r="R20" t="n">
-        <v>7080521</v>
+        <v>7080474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2571,7 +2562,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,10 +2589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389100</v>
+        <v>131389060</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,21 +2600,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2633,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457233</v>
+        <v>456972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080474</v>
+        <v>7080521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,7 +2664,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2700,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389083</v>
+        <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2711,19 +2702,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2731,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457266</v>
+        <v>456959</v>
       </c>
       <c r="R22" t="n">
-        <v>7080540</v>
+        <v>7080532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2767,6 +2762,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389099</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389085</v>
+        <v>131389048</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,19 +988,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1008,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457010</v>
+        <v>457237</v>
       </c>
       <c r="R5" t="n">
-        <v>7080480</v>
+        <v>7080435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,6 +1048,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389048</v>
+        <v>131389085</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,23 +1090,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1105,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457237</v>
+        <v>457010</v>
       </c>
       <c r="R6" t="n">
-        <v>7080435</v>
+        <v>7080480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,11 +1146,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131389097</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>131389047</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>131389044</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131389045</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B13" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,30 +1786,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R13" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,6 +1854,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1868,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,42 +1896,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R14" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1952,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,7 +1981,7 @@
         <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>131389053</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>131389054</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389083</v>
+        <v>131389100</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,19 +2405,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2425,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457266</v>
+        <v>457233</v>
       </c>
       <c r="R19" t="n">
-        <v>7080540</v>
+        <v>7080474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,6 +2465,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389100</v>
+        <v>131389060</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,21 +2507,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2531,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457233</v>
+        <v>456972</v>
       </c>
       <c r="R20" t="n">
-        <v>7080474</v>
+        <v>7080521</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2571,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,10 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389060</v>
+        <v>131389061</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456972</v>
+        <v>456959</v>
       </c>
       <c r="R21" t="n">
-        <v>7080521</v>
+        <v>7080532</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389061</v>
+        <v>131389083</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,23 +2711,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2726,10 +2731,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456959</v>
+        <v>457266</v>
       </c>
       <c r="R22" t="n">
-        <v>7080532</v>
+        <v>7080540</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2762,11 +2767,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389048</v>
+        <v>131389085</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,23 +988,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1012,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457237</v>
+        <v>457010</v>
       </c>
       <c r="R5" t="n">
-        <v>7080435</v>
+        <v>7080480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,11 +1044,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389085</v>
+        <v>131389048</v>
       </c>
       <c r="B6" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,19 +1081,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1110,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457010</v>
+        <v>457237</v>
       </c>
       <c r="R6" t="n">
-        <v>7080480</v>
+        <v>7080435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1141,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,23 +2405,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2429,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R19" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2461,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389060</v>
+        <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,21 +2498,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2531,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456972</v>
+        <v>457233</v>
       </c>
       <c r="R20" t="n">
-        <v>7080521</v>
+        <v>7080474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2571,7 +2562,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,7 +2589,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389061</v>
+        <v>131389060</v>
       </c>
       <c r="B21" t="n">
         <v>57887</v>
@@ -2633,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456959</v>
+        <v>456972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080532</v>
+        <v>7080521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389083</v>
+        <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2711,19 +2702,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2731,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457266</v>
+        <v>456959</v>
       </c>
       <c r="R22" t="n">
-        <v>7080540</v>
+        <v>7080532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2767,6 +2762,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389099</v>
+        <v>131389048</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,21 +886,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457168</v>
+        <v>457237</v>
       </c>
       <c r="R4" t="n">
-        <v>7080505</v>
+        <v>7080435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389048</v>
+        <v>131389099</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457237</v>
+        <v>457168</v>
       </c>
       <c r="R6" t="n">
-        <v>7080435</v>
+        <v>7080505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,42 +1786,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R13" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,11 +1842,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1885,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,30 +1879,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R14" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389048</v>
+        <v>131389085</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,23 +886,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457237</v>
+        <v>457010</v>
       </c>
       <c r="R4" t="n">
-        <v>7080435</v>
+        <v>7080480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,11 +942,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389085</v>
+        <v>131389099</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,19 +979,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1008,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457010</v>
+        <v>457168</v>
       </c>
       <c r="R5" t="n">
-        <v>7080480</v>
+        <v>7080505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,6 +1039,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389099</v>
+        <v>131389048</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457168</v>
+        <v>457237</v>
       </c>
       <c r="R6" t="n">
-        <v>7080505</v>
+        <v>7080435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131389097</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389047</v>
+        <v>131389044</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457342</v>
+        <v>457358</v>
       </c>
       <c r="R10" t="n">
-        <v>7080396</v>
+        <v>7080415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389044</v>
+        <v>131389045</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457358</v>
+        <v>457287</v>
       </c>
       <c r="R11" t="n">
-        <v>7080415</v>
+        <v>7080550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389045</v>
+        <v>131389047</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457287</v>
+        <v>457342</v>
       </c>
       <c r="R12" t="n">
-        <v>7080550</v>
+        <v>7080396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,30 +1786,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R13" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,6 +1854,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1868,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,42 +1896,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R14" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1952,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,7 +1981,7 @@
         <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389053</v>
+        <v>131389054</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457007</v>
+        <v>457005</v>
       </c>
       <c r="R17" t="n">
-        <v>7080483</v>
+        <v>7080485</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131389054</v>
+        <v>131389053</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457005</v>
+        <v>457007</v>
       </c>
       <c r="R18" t="n">
-        <v>7080485</v>
+        <v>7080483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389083</v>
+        <v>131389100</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,19 +2405,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2425,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457266</v>
+        <v>457233</v>
       </c>
       <c r="R19" t="n">
-        <v>7080540</v>
+        <v>7080474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,6 +2465,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,23 +2507,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2522,10 +2527,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R20" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,11 +2563,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2592,7 +2592,7 @@
         <v>131389060</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389097</v>
+        <v>131389047</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457310</v>
+        <v>457342</v>
       </c>
       <c r="R9" t="n">
-        <v>7080547</v>
+        <v>7080396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389047</v>
+        <v>131389097</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457342</v>
+        <v>457310</v>
       </c>
       <c r="R12" t="n">
-        <v>7080396</v>
+        <v>7080547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,42 +1786,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R13" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,11 +1842,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1885,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,30 +1879,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R14" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389054</v>
+        <v>131389053</v>
       </c>
       <c r="B17" t="n">
         <v>57888</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457005</v>
+        <v>457007</v>
       </c>
       <c r="R17" t="n">
-        <v>7080485</v>
+        <v>7080483</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131389053</v>
+        <v>131389054</v>
       </c>
       <c r="B18" t="n">
         <v>57888</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457007</v>
+        <v>457005</v>
       </c>
       <c r="R18" t="n">
-        <v>7080483</v>
+        <v>7080485</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -1367,7 +1367,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389047</v>
+        <v>131389044</v>
       </c>
       <c r="B9" t="n">
         <v>57888</v>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457342</v>
+        <v>457358</v>
       </c>
       <c r="R9" t="n">
-        <v>7080396</v>
+        <v>7080415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389044</v>
+        <v>131389097</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457358</v>
+        <v>457310</v>
       </c>
       <c r="R10" t="n">
-        <v>7080415</v>
+        <v>7080547</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389045</v>
+        <v>131389047</v>
       </c>
       <c r="B11" t="n">
         <v>57888</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457287</v>
+        <v>457342</v>
       </c>
       <c r="R11" t="n">
-        <v>7080550</v>
+        <v>7080396</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389097</v>
+        <v>131389045</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457310</v>
+        <v>457287</v>
       </c>
       <c r="R12" t="n">
-        <v>7080547</v>
+        <v>7080550</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,23 +2405,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2429,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R19" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2461,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389083</v>
+        <v>131389061</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,19 +2498,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457266</v>
+        <v>456959</v>
       </c>
       <c r="R20" t="n">
-        <v>7080540</v>
+        <v>7080532</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,6 +2558,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389060</v>
+        <v>131389100</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456972</v>
+        <v>457233</v>
       </c>
       <c r="R21" t="n">
-        <v>7080521</v>
+        <v>7080474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389061</v>
+        <v>131389060</v>
       </c>
       <c r="B22" t="n">
         <v>57888</v>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456959</v>
+        <v>456972</v>
       </c>
       <c r="R22" t="n">
-        <v>7080532</v>
+        <v>7080521</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389085</v>
+        <v>131389099</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,19 +886,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -906,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457010</v>
+        <v>457168</v>
       </c>
       <c r="R4" t="n">
-        <v>7080480</v>
+        <v>7080505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,6 +946,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389099</v>
+        <v>131389085</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -979,23 +988,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457168</v>
+        <v>457010</v>
       </c>
       <c r="R5" t="n">
-        <v>7080505</v>
+        <v>7080480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,11 +1044,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1073,7 @@
         <v>131389048</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389044</v>
+        <v>131389047</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457358</v>
+        <v>457342</v>
       </c>
       <c r="R9" t="n">
-        <v>7080415</v>
+        <v>7080396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389097</v>
+        <v>131389044</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457310</v>
+        <v>457358</v>
       </c>
       <c r="R10" t="n">
-        <v>7080547</v>
+        <v>7080415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389047</v>
+        <v>131389045</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457342</v>
+        <v>457287</v>
       </c>
       <c r="R11" t="n">
-        <v>7080396</v>
+        <v>7080550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389045</v>
+        <v>131389097</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457287</v>
+        <v>457310</v>
       </c>
       <c r="R12" t="n">
-        <v>7080550</v>
+        <v>7080547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,7 +1778,7 @@
         <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389043</v>
+        <v>131389059</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,24 +2007,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456992</v>
+        <v>456981</v>
       </c>
       <c r="R15" t="n">
-        <v>7080517</v>
+        <v>7080514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,14 +2053,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2088,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389059</v>
+        <v>131389043</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,16 +2109,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456981</v>
+        <v>456992</v>
       </c>
       <c r="R16" t="n">
-        <v>7080514</v>
+        <v>7080517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>131389053</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>131389054</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389061</v>
+        <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456959</v>
+        <v>457233</v>
       </c>
       <c r="R20" t="n">
-        <v>7080532</v>
+        <v>7080474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389100</v>
+        <v>131389060</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457233</v>
+        <v>456972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080474</v>
+        <v>7080521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389060</v>
+        <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456972</v>
+        <v>456959</v>
       </c>
       <c r="R22" t="n">
-        <v>7080521</v>
+        <v>7080532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389099</v>
+        <v>131389085</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>91842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,23 +886,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457168</v>
+        <v>457010</v>
       </c>
       <c r="R4" t="n">
-        <v>7080505</v>
+        <v>7080480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,11 +942,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389085</v>
+        <v>131389048</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,19 +979,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1008,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457010</v>
+        <v>457237</v>
       </c>
       <c r="R5" t="n">
-        <v>7080480</v>
+        <v>7080435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,6 +1039,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389048</v>
+        <v>131389099</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457237</v>
+        <v>457168</v>
       </c>
       <c r="R6" t="n">
-        <v>7080435</v>
+        <v>7080505</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131389047</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>131389044</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>131389045</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>131389097</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389059</v>
+        <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,16 +2007,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456981</v>
+        <v>456992</v>
       </c>
       <c r="R15" t="n">
-        <v>7080514</v>
+        <v>7080517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,14 +2061,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2080,10 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389043</v>
+        <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,24 +2117,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456992</v>
+        <v>456981</v>
       </c>
       <c r="R16" t="n">
-        <v>7080517</v>
+        <v>7080514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>131389053</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>131389054</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389100</v>
+        <v>131389060</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457233</v>
+        <v>456972</v>
       </c>
       <c r="R20" t="n">
-        <v>7080474</v>
+        <v>7080521</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389060</v>
+        <v>131389061</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456972</v>
+        <v>456959</v>
       </c>
       <c r="R21" t="n">
-        <v>7080521</v>
+        <v>7080532</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389061</v>
+        <v>131389100</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456959</v>
+        <v>457233</v>
       </c>
       <c r="R22" t="n">
-        <v>7080532</v>
+        <v>7080474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -2487,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389060</v>
+        <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456972</v>
+        <v>457233</v>
       </c>
       <c r="R20" t="n">
-        <v>7080521</v>
+        <v>7080474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,7 +2589,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389061</v>
+        <v>131389060</v>
       </c>
       <c r="B21" t="n">
         <v>57892</v>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456959</v>
+        <v>456972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080532</v>
+        <v>7080521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389100</v>
+        <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457233</v>
+        <v>456959</v>
       </c>
       <c r="R22" t="n">
-        <v>7080474</v>
+        <v>7080532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389085</v>
+        <v>131389099</v>
       </c>
       <c r="B4" t="n">
-        <v>91842</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,19 +886,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -906,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457010</v>
+        <v>457168</v>
       </c>
       <c r="R4" t="n">
-        <v>7080480</v>
+        <v>7080505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,6 +946,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389048</v>
+        <v>131389085</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -979,23 +988,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457237</v>
+        <v>457010</v>
       </c>
       <c r="R5" t="n">
-        <v>7080435</v>
+        <v>7080480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,11 +1044,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389099</v>
+        <v>131389048</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,21 +1081,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457168</v>
+        <v>457237</v>
       </c>
       <c r="R6" t="n">
-        <v>7080505</v>
+        <v>7080435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389047</v>
+        <v>131389097</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457342</v>
+        <v>457310</v>
       </c>
       <c r="R9" t="n">
-        <v>7080396</v>
+        <v>7080547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389044</v>
+        <v>131389047</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457358</v>
+        <v>457342</v>
       </c>
       <c r="R10" t="n">
-        <v>7080415</v>
+        <v>7080396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389045</v>
+        <v>131389044</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457287</v>
+        <v>457358</v>
       </c>
       <c r="R11" t="n">
-        <v>7080550</v>
+        <v>7080415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389097</v>
+        <v>131389045</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457310</v>
+        <v>457287</v>
       </c>
       <c r="R12" t="n">
-        <v>7080547</v>
+        <v>7080550</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,7 +1778,7 @@
         <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>131389053</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>131389054</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389083</v>
+        <v>131389100</v>
       </c>
       <c r="B19" t="n">
-        <v>91842</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,19 +2405,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2425,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457266</v>
+        <v>457233</v>
       </c>
       <c r="R19" t="n">
-        <v>7080540</v>
+        <v>7080474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,6 +2465,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,23 +2507,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2522,10 +2527,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R20" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,11 +2563,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2592,7 +2592,7 @@
         <v>131389060</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,23 +2405,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2429,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R19" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2461,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389083</v>
+        <v>131389060</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,19 +2498,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457266</v>
+        <v>456972</v>
       </c>
       <c r="R20" t="n">
-        <v>7080540</v>
+        <v>7080521</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,6 +2558,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,7 +2589,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389060</v>
+        <v>131389061</v>
       </c>
       <c r="B21" t="n">
         <v>57898</v>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456972</v>
+        <v>456959</v>
       </c>
       <c r="R21" t="n">
-        <v>7080521</v>
+        <v>7080532</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389061</v>
+        <v>131389100</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456959</v>
+        <v>457233</v>
       </c>
       <c r="R22" t="n">
-        <v>7080532</v>
+        <v>7080474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -1978,7 +1978,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389043</v>
+        <v>131389059</v>
       </c>
       <c r="B15" t="n">
         <v>57898</v>
@@ -2007,24 +2007,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456992</v>
+        <v>456981</v>
       </c>
       <c r="R15" t="n">
-        <v>7080517</v>
+        <v>7080514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,14 +2053,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2088,7 +2080,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389059</v>
+        <v>131389043</v>
       </c>
       <c r="B16" t="n">
         <v>57898</v>
@@ -2117,16 +2109,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456981</v>
+        <v>456992</v>
       </c>
       <c r="R16" t="n">
-        <v>7080514</v>
+        <v>7080517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389060</v>
+        <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,21 +2498,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456972</v>
+        <v>457233</v>
       </c>
       <c r="R20" t="n">
-        <v>7080521</v>
+        <v>7080474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,7 +2589,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389061</v>
+        <v>131389060</v>
       </c>
       <c r="B21" t="n">
         <v>57898</v>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456959</v>
+        <v>456972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080532</v>
+        <v>7080521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389100</v>
+        <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457233</v>
+        <v>456959</v>
       </c>
       <c r="R22" t="n">
-        <v>7080474</v>
+        <v>7080532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389097</v>
+        <v>131389047</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457310</v>
+        <v>457342</v>
       </c>
       <c r="R9" t="n">
-        <v>7080547</v>
+        <v>7080396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389047</v>
+        <v>131389044</v>
       </c>
       <c r="B10" t="n">
         <v>57898</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457342</v>
+        <v>457358</v>
       </c>
       <c r="R10" t="n">
-        <v>7080396</v>
+        <v>7080415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389044</v>
+        <v>131389045</v>
       </c>
       <c r="B11" t="n">
         <v>57898</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457358</v>
+        <v>457287</v>
       </c>
       <c r="R11" t="n">
-        <v>7080415</v>
+        <v>7080550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389045</v>
+        <v>131389097</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457287</v>
+        <v>457310</v>
       </c>
       <c r="R12" t="n">
-        <v>7080550</v>
+        <v>7080547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B13" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,30 +1786,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R13" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,6 +1854,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1868,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,42 +1896,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R14" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1952,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,7 +1978,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389059</v>
+        <v>131389043</v>
       </c>
       <c r="B15" t="n">
         <v>57898</v>
@@ -2007,16 +2007,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456981</v>
+        <v>456992</v>
       </c>
       <c r="R15" t="n">
-        <v>7080514</v>
+        <v>7080517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,14 +2061,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2080,7 +2088,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389043</v>
+        <v>131389059</v>
       </c>
       <c r="B16" t="n">
         <v>57898</v>
@@ -2109,24 +2117,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456992</v>
+        <v>456981</v>
       </c>
       <c r="R16" t="n">
-        <v>7080517</v>
+        <v>7080514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,14 +2163,14 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -977,10 +977,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389085</v>
+        <v>131389048</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,19 +988,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1008,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457010</v>
+        <v>457237</v>
       </c>
       <c r="R5" t="n">
-        <v>7080480</v>
+        <v>7080435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,6 +1048,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1070,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389048</v>
+        <v>131389085</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,23 +1090,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1105,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457237</v>
+        <v>457010</v>
       </c>
       <c r="R6" t="n">
-        <v>7080435</v>
+        <v>7080480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,11 +1146,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389047</v>
+        <v>131389097</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457342</v>
+        <v>457310</v>
       </c>
       <c r="R9" t="n">
-        <v>7080396</v>
+        <v>7080547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389044</v>
+        <v>131389047</v>
       </c>
       <c r="B10" t="n">
         <v>57898</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457358</v>
+        <v>457342</v>
       </c>
       <c r="R10" t="n">
-        <v>7080415</v>
+        <v>7080396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389045</v>
+        <v>131389044</v>
       </c>
       <c r="B11" t="n">
         <v>57898</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457287</v>
+        <v>457358</v>
       </c>
       <c r="R11" t="n">
-        <v>7080550</v>
+        <v>7080415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389097</v>
+        <v>131389045</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457310</v>
+        <v>457287</v>
       </c>
       <c r="R12" t="n">
-        <v>7080547</v>
+        <v>7080550</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>91848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,42 +1786,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R13" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,11 +1842,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1885,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>91848</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,30 +1879,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R14" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,6 +1947,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389083</v>
+        <v>131389100</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,19 +2405,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2425,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457266</v>
+        <v>457233</v>
       </c>
       <c r="R19" t="n">
-        <v>7080540</v>
+        <v>7080474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,6 +2465,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2487,10 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2498,23 +2507,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2522,10 +2527,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R20" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,11 +2563,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>131389099</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>131389048</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131389085</v>
       </c>
       <c r="B6" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131389097</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389047</v>
+        <v>131389045</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457342</v>
+        <v>457287</v>
       </c>
       <c r="R10" t="n">
-        <v>7080396</v>
+        <v>7080550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1574,7 +1574,7 @@
         <v>131389044</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389045</v>
+        <v>131389047</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457287</v>
+        <v>457342</v>
       </c>
       <c r="R12" t="n">
-        <v>7080550</v>
+        <v>7080396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,7 +1778,7 @@
         <v>131389086</v>
       </c>
       <c r="B13" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>131389046</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389053</v>
+        <v>131389054</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457007</v>
+        <v>457005</v>
       </c>
       <c r="R17" t="n">
-        <v>7080483</v>
+        <v>7080485</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131389054</v>
+        <v>131389053</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457005</v>
+        <v>457007</v>
       </c>
       <c r="R18" t="n">
-        <v>7080485</v>
+        <v>7080483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389100</v>
+        <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>91849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2405,23 +2405,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2429,10 +2425,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457233</v>
+        <v>457266</v>
       </c>
       <c r="R19" t="n">
-        <v>7080474</v>
+        <v>7080540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,11 +2461,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2496,10 +2487,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389083</v>
+        <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,19 +2498,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457266</v>
+        <v>457233</v>
       </c>
       <c r="R20" t="n">
-        <v>7080540</v>
+        <v>7080474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,6 +2558,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389060</v>
+        <v>131389061</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456972</v>
+        <v>456959</v>
       </c>
       <c r="R21" t="n">
-        <v>7080521</v>
+        <v>7080532</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389061</v>
+        <v>131389060</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456959</v>
+        <v>456972</v>
       </c>
       <c r="R22" t="n">
-        <v>7080532</v>
+        <v>7080521</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131389082</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389099</v>
+        <v>131389085</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>91852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -886,23 +886,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +906,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457168</v>
+        <v>457010</v>
       </c>
       <c r="R4" t="n">
-        <v>7080505</v>
+        <v>7080480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,11 +942,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,10 +968,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389048</v>
+        <v>131389099</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -988,21 +979,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1012,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457237</v>
+        <v>457168</v>
       </c>
       <c r="R5" t="n">
-        <v>7080435</v>
+        <v>7080505</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,7 +1043,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,10 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389085</v>
+        <v>131389048</v>
       </c>
       <c r="B6" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,19 +1081,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1110,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457010</v>
+        <v>457237</v>
       </c>
       <c r="R6" t="n">
-        <v>7080480</v>
+        <v>7080435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1141,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1175,7 @@
         <v>131389084</v>
       </c>
       <c r="B7" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131389055</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389097</v>
+        <v>131389047</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457310</v>
+        <v>457342</v>
       </c>
       <c r="R9" t="n">
-        <v>7080547</v>
+        <v>7080396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389045</v>
+        <v>131389044</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457287</v>
+        <v>457358</v>
       </c>
       <c r="R10" t="n">
-        <v>7080550</v>
+        <v>7080415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389044</v>
+        <v>131389045</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457358</v>
+        <v>457287</v>
       </c>
       <c r="R11" t="n">
-        <v>7080415</v>
+        <v>7080550</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389047</v>
+        <v>131389097</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457342</v>
+        <v>457310</v>
       </c>
       <c r="R12" t="n">
-        <v>7080396</v>
+        <v>7080547</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389086</v>
+        <v>131389046</v>
       </c>
       <c r="B13" t="n">
-        <v>91849</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,30 +1786,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456992</v>
+        <v>457268</v>
       </c>
       <c r="R13" t="n">
-        <v>7080516</v>
+        <v>7080539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,6 +1854,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1868,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389046</v>
+        <v>131389086</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>91852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,42 +1896,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457268</v>
+        <v>456992</v>
       </c>
       <c r="R14" t="n">
-        <v>7080539</v>
+        <v>7080516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,11 +1952,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,7 +1981,7 @@
         <v>131389043</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>131389059</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389054</v>
+        <v>131389053</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457005</v>
+        <v>457007</v>
       </c>
       <c r="R17" t="n">
-        <v>7080485</v>
+        <v>7080483</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131389053</v>
+        <v>131389054</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457007</v>
+        <v>457005</v>
       </c>
       <c r="R18" t="n">
-        <v>7080483</v>
+        <v>7080485</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
         <v>131389083</v>
       </c>
       <c r="B19" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>131389100</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389061</v>
+        <v>131389060</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456959</v>
+        <v>456972</v>
       </c>
       <c r="R21" t="n">
-        <v>7080532</v>
+        <v>7080521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389060</v>
+        <v>131389061</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456972</v>
+        <v>456959</v>
       </c>
       <c r="R22" t="n">
-        <v>7080521</v>
+        <v>7080532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2796,7 +2796,7 @@
         <v>131389098</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532064</v>
+        <v>131389097</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457331</v>
+        <v>457310</v>
       </c>
       <c r="R2" t="n">
-        <v>7080491</v>
+        <v>7080547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,30 +777,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389082</v>
+        <v>131389098</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -813,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457338</v>
+        <v>457039</v>
       </c>
       <c r="R3" t="n">
-        <v>7080487</v>
+        <v>7080517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389048</v>
+        <v>131389099</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457237</v>
+        <v>457168</v>
       </c>
       <c r="R4" t="n">
-        <v>7080435</v>
+        <v>7080505</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,14 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389099</v>
+        <v>131389100</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1012,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457168</v>
+        <v>457233</v>
       </c>
       <c r="R5" t="n">
-        <v>7080505</v>
+        <v>7080474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,30 +1083,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131389085</v>
+        <v>131389101</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1110,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457010</v>
+        <v>457115</v>
       </c>
       <c r="R6" t="n">
-        <v>7080480</v>
+        <v>7080430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,6 +1154,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mycket Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1172,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131389084</v>
+        <v>121532064</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,19 +1196,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1203,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457252</v>
+        <v>457331</v>
       </c>
       <c r="R7" t="n">
-        <v>7080519</v>
+        <v>7080491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1233,12 +1250,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131389055</v>
+        <v>131389043</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,16 +1316,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457004</v>
+        <v>456992</v>
       </c>
       <c r="R8" t="n">
-        <v>7080486</v>
+        <v>7080517</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,14 +1370,14 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1367,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131389047</v>
+        <v>131389044</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457342</v>
+        <v>457358</v>
       </c>
       <c r="R9" t="n">
-        <v>7080396</v>
+        <v>7080415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131389044</v>
+        <v>131389045</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457358</v>
+        <v>457287</v>
       </c>
       <c r="R10" t="n">
-        <v>7080415</v>
+        <v>7080550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,7 +1574,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131389045</v>
+        <v>131389046</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1600,16 +1630,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457287</v>
+        <v>457268</v>
       </c>
       <c r="R11" t="n">
-        <v>7080550</v>
+        <v>7080539</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,7 +1684,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131389097</v>
+        <v>131389047</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1722,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457310</v>
+        <v>457342</v>
       </c>
       <c r="R12" t="n">
-        <v>7080547</v>
+        <v>7080396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,7 +1786,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131389046</v>
+        <v>131389048</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,24 +1842,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457268</v>
+        <v>457237</v>
       </c>
       <c r="R13" t="n">
-        <v>7080539</v>
+        <v>7080435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1888,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bohål ca 1,8m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1885,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131389086</v>
+        <v>131389049</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,19 +1926,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1916,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456992</v>
+        <v>457180</v>
       </c>
       <c r="R14" t="n">
-        <v>7080516</v>
+        <v>7080431</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,6 +1986,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131389043</v>
+        <v>131389050</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,24 +2046,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tretjärnrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456992</v>
+        <v>457143</v>
       </c>
       <c r="R15" t="n">
-        <v>7080517</v>
+        <v>7080428</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,14 +2092,14 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Bohål? Ca 5m upp i grantickerötad granhögstubbe</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2088,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131389059</v>
+        <v>131389051</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2123,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456981</v>
+        <v>457052</v>
       </c>
       <c r="R16" t="n">
-        <v>7080514</v>
+        <v>7080441</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131389053</v>
+        <v>131389052</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2225,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457007</v>
+        <v>457039</v>
       </c>
       <c r="R17" t="n">
-        <v>7080483</v>
+        <v>7080446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131389054</v>
+        <v>131389053</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457005</v>
+        <v>457007</v>
       </c>
       <c r="R18" t="n">
-        <v>7080485</v>
+        <v>7080483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131389061</v>
+        <v>131389054</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456959</v>
+        <v>457005</v>
       </c>
       <c r="R19" t="n">
-        <v>7080532</v>
+        <v>7080485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131389100</v>
+        <v>131389055</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,21 +2538,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2531,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457233</v>
+        <v>457004</v>
       </c>
       <c r="R20" t="n">
-        <v>7080474</v>
+        <v>7080486</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2571,7 +2602,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131389083</v>
+        <v>131389056</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,19 +2640,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2629,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457266</v>
+        <v>457002</v>
       </c>
       <c r="R21" t="n">
-        <v>7080540</v>
+        <v>7080484</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,6 +2700,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2691,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131389060</v>
+        <v>131389057</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>456972</v>
+        <v>456989</v>
       </c>
       <c r="R22" t="n">
-        <v>7080521</v>
+        <v>7080503</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,10 +2833,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131389098</v>
+        <v>131389058</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2804,21 +2844,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2828,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457039</v>
+        <v>456987</v>
       </c>
       <c r="R23" t="n">
-        <v>7080517</v>
+        <v>7080504</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2868,7 +2908,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2892,6 +2932,516 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131389059</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>456981</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7080514</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131389060</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>456972</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7080521</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131389061</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>456959</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7080532</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131389062</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>456956</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7080529</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131389063</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tretjärnrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>456935</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7080540</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3501-2026 artfynd.xlsx
+++ b/artfynd/A 3501-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389097</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389098</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389099</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389101</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121532064</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389043</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389044</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389045</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389046</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1810,6 +1865,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389048</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389049</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389050</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389051</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389052</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389053</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389054</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389055</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2728,6 +2828,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389056</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2830,6 +2935,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389057</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2932,6 +3042,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389058</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3034,6 +3149,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389059</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3136,6 +3256,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389060</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3238,6 +3363,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389061</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3340,6 +3470,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389062</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3442,8 +3577,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389063</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>